--- a/output/TEST_CLASSIC_stage_three_and_four.xlsx
+++ b/output/TEST_CLASSIC_stage_three_and_four.xlsx
@@ -184,94 +184,94 @@
     <t xml:space="preserve">Data Complete</t>
   </si>
   <si>
-    <t xml:space="preserve">&amp;id=1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=50</t>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=50</t>
   </si>
   <si>
     <t xml:space="preserve">record_id</t>
@@ -409,7 +409,7 @@
     <t xml:space="preserve">ctcae5:C57293</t>
   </si>
   <si>
-    <t xml:space="preserve">2025-09-05</t>
+    <t xml:space="preserve">2026-01-27</t>
   </si>
   <si>
     <t xml:space="preserve">2025-11-19 19:55:00</t>
@@ -481,10 +481,10 @@
     <t xml:space="preserve">IV</t>
   </si>
   <si>
-    <t xml:space="preserve">2018-11-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-07-15</t>
+    <t xml:space="preserve">2019-04-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-12-06</t>
   </si>
   <si>
     <t xml:space="preserve">Complete</t>
@@ -493,1362 +493,1362 @@
     <t xml:space="preserve">2</t>
   </si>
   <si>
-    <t xml:space="preserve">2024-02-08</t>
+    <t xml:space="preserve">2024-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-30 15:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-18 09:20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-20 14:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-16 08:36:17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-11 07:58:51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:14:28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05:11:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Does not have comma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">III</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-11-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">False</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-01-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-03-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-06 16:49:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-01-26 12:03:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-24 01:23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-06 14:42:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-31 02:53:51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">j</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04:30:38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05:31:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">has, ,comma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-03-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-03-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-07 09:43:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-13 01:07:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-05 14:51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-25 13:38:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-13 19:33:21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:55:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01:58:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incomplete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-09-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-03-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-01-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-15 17:58:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-17 00:09:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-01 08:17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-23 18:04:22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-09 09:25:04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:28:19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:34:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-12-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-10-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-23 16:21:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-01-23 19:06:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-14 18:53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-26 15:36:01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-04 00:04:04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:20:28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10:39:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019-08-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-11-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-01-24 04:32:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-28 00:27:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-09 16:16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-06 09:41:26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-14 10:51:13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">r</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04:45:29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23:42:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-02-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-01-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-02-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-11 16:05:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-07 22:34:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-29 07:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-01-13 16:45:06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-13 20:01:04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21:06:53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:03:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-10-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-08 17:34:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-03 07:48:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-08 02:58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-09 11:02:32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-23 16:17:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:52:03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:54:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-07-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-01-29 21:53:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-25 20:41:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-01 23:56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-22 01:57:43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-03 14:49:48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:46:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08:19:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-01-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-01-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-31 19:02:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-25 16:35:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-28 03:23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-10 07:36:26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-29 21:46:27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:08:46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10:31:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-04-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-03-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-25 00:25:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-31 20:49:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-01-11 02:52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-07 09:58:03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-15 01:06:38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:18:40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03:47:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-06-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-02-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-02-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-18 10:16:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-01-28 19:58:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-12 18:09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-20 02:27:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-23 16:34:27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:55:04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:11:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018-05-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018-07-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-02-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-18 21:40:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-11 10:43:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-14 06:22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-11 00:42:46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-18 13:31:57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:25:39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:56:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-10-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-02-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-19</t>
   </si>
   <si>
     <t xml:space="preserve">2024-04-08</t>
   </si>
   <si>
-    <t xml:space="preserve">2024-02-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-30 15:30:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-18 09:20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-20 14:45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-16 08:36:17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-11 07:58:51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:14:28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05:11:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Does not have comma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">III</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-06-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-03-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">False</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-06 16:49:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-26 12:03:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-24 01:23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-06 14:42:10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-31 02:53:51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">j</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04:30:38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05:31:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">has, ,comma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-11-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-11-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-07 09:43:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-13 01:07:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-05 14:51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-25 13:38:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-13 19:33:21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:55:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01:58:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incomplete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-05-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-10-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-11-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-15 17:58:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-17 00:09:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-01 08:17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-23 18:04:22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-09 09:25:04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.68</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07:28:19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:34:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-07-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-05-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-23 16:21:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-23 19:06:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-14 18:53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-26 15:36:01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-04 00:04:04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20:20:28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10:39:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2019-04-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-24 04:32:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-28 00:27:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-09 16:16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-06 09:41:26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-14 10:51:13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">r</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.76</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04:45:29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23:42:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-10-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-11 16:05:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-07 22:34:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-29 07:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-13 16:45:06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-13 20:01:04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21:06:53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12:03:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-02-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-28</t>
+    <t xml:space="preserve">2024-05-27 18:04:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-03 12:03:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-28 18:33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-10 02:19:53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-05 18:06:07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:47:28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03:44:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-12-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-01-24 13:38:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-03 17:20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-16 17:11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-08 06:36:29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-31 20:45:29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21:16:18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:23:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-06-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-10 01:04:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-07 06:29:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-11 22:09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-26 16:12:41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-01 19:01:19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13:50:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:08:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-03-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-02-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-20 19:01:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-12 21:20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-26 18:34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-27 14:40:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-17 03:39:21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:22:33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10:27:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018-08-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-01-05 10:18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-30 10:17:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-17 07:55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-11 00:10:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-26 21:55:40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:50:09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:45:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-10-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-19 04:17:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-20 03:51:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-01-13 04:19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-07 07:40:26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-01-01 12:40:08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:52:27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:53:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-03-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-02-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-02 22:15:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-06 02:20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-01-23 21:44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-01-12 02:14:49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-01-22 00:11:07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04:48:48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22:28:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-12-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36</t>
   </si>
   <si>
     <t xml:space="preserve">2024-03-18</t>
   </si>
   <si>
-    <t xml:space="preserve">2024-04-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-08 17:34:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-03 07:48:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-08 02:58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-09 11:02:32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-23 16:17:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">t</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:52:03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:54:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-01-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-02-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-29 21:53:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-25 20:41:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-01 23:56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-22 01:57:43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-03 14:49:48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">o</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:46:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08:19:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2019-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-01-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-11-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-31 19:02:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-25 16:35:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-28 03:23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-10 07:36:26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-29 21:46:27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:08:46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10:31:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-11-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-10-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-10-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-25 00:25:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-31 20:49:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-11 02:52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-07 09:58:03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-15 01:06:38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.91</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12:18:40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03:47:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-02-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-09-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-18 10:16:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-28 19:58:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-12 18:09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-20 02:27:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-23 16:34:27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:55:04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12:11:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2017-12-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2018-02-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25</t>
+    <t xml:space="preserve">2024-11-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-28 01:58:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-08 19:43:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-29 18:19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-21 06:16:37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-29 13:32:23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:46:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06:01:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018-11-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-01-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-02-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-18 22:10:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-30 12:53:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-23 12:24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-05 18:58:44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-10 07:40:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10:08:13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:42:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018-07-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019-01-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-28 06:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-29 16:19:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-18 06:11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-08 04:21:34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-07 14:42:56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:42:56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:54:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-08-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-02-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-27 03:35:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-07 19:07:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-12 05:54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-04 00:40:03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-02 22:07:27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01:14:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21:25:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-01-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-12-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-03 12:26:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-17 18:46:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-11 22:09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-16 14:28:21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-21 02:38:06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:43:54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-08-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2028-12-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-01-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-01 11:20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-03 03:37:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-12 10:36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-22 01:31:39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-08 06:55:22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:59:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22:18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-09-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-03-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-26 12:32:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-18 20:39:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-08 22:51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-20 11:53:32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-27 01:15:17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23:47:40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-09-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-24 18:46:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-20 18:29:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-13 22:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-17 13:49:19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-09 08:27:12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:26:34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:32:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-01-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-04-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-20</t>
   </si>
   <si>
     <t xml:space="preserve">2024-09-11</t>
   </si>
   <si>
-    <t xml:space="preserve">2024-05-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-18 21:40:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-11 10:43:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-14 06:22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-11 00:42:46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-18 13:31:57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20:25:39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:56:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-09-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-11-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-27 18:04:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-03 12:03:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-28 18:33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-10 02:19:53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-05 18:06:07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">00:47:28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03:44:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-07-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-01-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-24 13:38:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-03 17:20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-16 17:11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-08 06:36:29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-31 20:45:29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21:16:18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:23:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-01-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-11-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-10 01:04:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-07 06:29:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-11 22:09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-26 16:12:41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-01 19:01:19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13:50:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:08:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-10-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-12-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-20 19:01:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-12 21:20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-26 18:34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-27 14:40:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-17 03:39:21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07:22:33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10:27:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2018-03-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2019-02-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-11-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-12-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-12-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-05 10:18:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-30 10:17:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-17 07:55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-11 00:10:45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-26 21:55:40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20:50:09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07:45:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-05-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-09-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-12-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-11-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-19 04:17:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-20 03:51:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-13 04:19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-07 07:40:26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-01-01 12:40:08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:52:27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:53:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-10-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-11-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-02 22:15:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-06 02:20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-23 21:44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-12 02:14:49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-22 00:11:07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">k</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04:48:48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22:28:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-08-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-10-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-10-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-28 01:58:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-08 19:43:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-29 18:19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-21 06:16:37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-29 13:32:23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.98</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:46:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06:01:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2018-06-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-18 22:10:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-30 12:53:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-23 12:24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-05 18:58:44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-10 07:40:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10:08:13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:42:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2018-02-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2018-08-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-12-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-28 06:30:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-29 16:19:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-18 06:11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-08 04:21:34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-07 14:42:56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07:42:56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:54:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-04-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-10-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-27 03:35:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-07 19:07:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-12 05:54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-04 00:40:03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-02 22:07:27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01:14:45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21:25:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2019-09-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-07-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-03 12:26:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-17 18:46:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-11 22:09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-16 14:28:21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-21 02:38:06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:43:54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-03-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2028-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-01 11:20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-03 03:37:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-12 10:36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-22 01:31:39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-08 06:55:22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:59:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22:18:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-01-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-04-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-26 12:32:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-18 20:39:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-08 22:51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-20 11:53:32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-27 01:15:17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">u</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23:47:40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-05-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-24 18:46:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-20 18:29:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-13 22:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-17 13:49:19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-09 08:27:12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20:26:34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20:32:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-08-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-11-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-20</t>
-  </si>
-  <si>
     <t xml:space="preserve">2024-04-27 17:59:00</t>
   </si>
   <si>
@@ -1879,10 +1879,10 @@
     <t xml:space="preserve">117</t>
   </si>
   <si>
-    <t xml:space="preserve">2020-03-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-06-01</t>
+    <t xml:space="preserve">2020-08-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-10-23</t>
   </si>
   <si>
     <t xml:space="preserve">form_name</t>
@@ -2728,7 +2728,7 @@
     <t xml:space="preserve">last_save_time</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-06 08:05:01.658129</t>
+    <t xml:space="preserve">2026-05-10 15:18:59.301426</t>
   </si>
   <si>
     <t xml:space="preserve">final_form_tab_names</t>
